--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Product Code</t>
   </si>
@@ -38,10 +38,55 @@
     <t>Price</t>
   </si>
   <si>
-    <t>17256esimbl</t>
+    <t>Image URL</t>
+  </si>
+  <si>
+    <t>17256bl</t>
   </si>
   <si>
     <t>iPhone 17 256GB Black (eSim)</t>
+  </si>
+  <si>
+    <t>17256wh</t>
+  </si>
+  <si>
+    <t>iPhone 17 256GB White (eSim)</t>
+  </si>
+  <si>
+    <t>17256blu</t>
+  </si>
+  <si>
+    <t>iPhone 17 256GB Blue (eSim)</t>
+  </si>
+  <si>
+    <t>17256sg</t>
+  </si>
+  <si>
+    <t>iPhone 17 256GB Sage (eSim)</t>
+  </si>
+  <si>
+    <t>17256lv</t>
+  </si>
+  <si>
+    <t>iPhone 17 256GB Lavender (eSim)</t>
+  </si>
+  <si>
+    <t>17512bl</t>
+  </si>
+  <si>
+    <t>iPhone 17 512GB Black (eSim)</t>
+  </si>
+  <si>
+    <t>17512wh</t>
+  </si>
+  <si>
+    <t>iPhone 17 512GB White (eSim)</t>
+  </si>
+  <si>
+    <t>17512sg</t>
+  </si>
+  <si>
+    <t>iPhone 17 512GB Sage (eSim)</t>
   </si>
 </sst>
 </file>
@@ -63,6 +108,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -517,19 +563,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -538,7 +584,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,8 +708,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1010,34 +1062,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="14.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="13.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" ht="30" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
         <v>60100</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>61300</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>60400</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2">
+        <v>60800</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2">
+        <v>60800</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2">
+        <v>76000</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2">
+        <v>75200</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2">
+        <v>80000</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,66 +27,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Product Code</t>
-  </si>
-  <si>
-    <t>Product Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Color</t>
   </si>
   <si>
     <t>Price</t>
   </si>
   <si>
-    <t>Image URL</t>
-  </si>
-  <si>
-    <t>17256bl</t>
-  </si>
-  <si>
-    <t>iPhone 17 256GB Black (eSim)</t>
-  </si>
-  <si>
-    <t>17256wh</t>
-  </si>
-  <si>
-    <t>iPhone 17 256GB White (eSim)</t>
-  </si>
-  <si>
-    <t>17256blu</t>
-  </si>
-  <si>
-    <t>iPhone 17 256GB Blue (eSim)</t>
-  </si>
-  <si>
-    <t>17256sg</t>
-  </si>
-  <si>
-    <t>iPhone 17 256GB Sage (eSim)</t>
-  </si>
-  <si>
-    <t>17256lv</t>
-  </si>
-  <si>
-    <t>iPhone 17 256GB Lavender (eSim)</t>
-  </si>
-  <si>
-    <t>17512bl</t>
-  </si>
-  <si>
-    <t>iPhone 17 512GB Black (eSim)</t>
-  </si>
-  <si>
-    <t>17512wh</t>
-  </si>
-  <si>
-    <t>iPhone 17 512GB White (eSim)</t>
-  </si>
-  <si>
-    <t>17512sg</t>
-  </si>
-  <si>
-    <t>iPhone 17 512GB Sage (eSim)</t>
+    <t>Emoji ID</t>
+  </si>
+  <si>
+    <t>iPhone 17</t>
+  </si>
+  <si>
+    <t>256GB</t>
+  </si>
+  <si>
+    <t>eSIM</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>&lt;tg-emoji emoji-id="5337119983430304580"&gt;☺&lt;/tg-emoji&gt;</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>&lt;tg-emoji emoji-id="5336860691959674526"&gt;☺&lt;/tg-emoji&gt;</t>
   </si>
 </sst>
 </file>
@@ -99,7 +78,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +88,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -578,140 +565,146 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1062,15 +1055,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="13.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1083,101 +1076,87 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="120" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>60100</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>63000</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="120" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2">
-        <v>61300</v>
-      </c>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2">
+        <v>64100</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2">
-        <v>60400</v>
-      </c>
-      <c r="D4" s="2"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2">
-        <v>60800</v>
-      </c>
-      <c r="D5" s="2"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
-        <v>60800</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2">
-        <v>76000</v>
-      </c>
-      <c r="D7" s="2"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2">
-        <v>75200</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2">
-        <v>80000</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Model</t>
   </si>
@@ -56,16 +56,49 @@
     <t>eSIM</t>
   </si>
   <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>&lt;tg-emoji emoji-id="5337119983430304580"&gt;☺&lt;/tg-emoji&gt;</t>
+    <t>Blue</t>
   </si>
   <si>
     <t>White</t>
   </si>
   <si>
-    <t>&lt;tg-emoji emoji-id="5336860691959674526"&gt;☺&lt;/tg-emoji&gt;</t>
+    <t>5337119983430304580</t>
+  </si>
+  <si>
+    <t>iPhone 18</t>
+  </si>
+  <si>
+    <t>257GB</t>
+  </si>
+  <si>
+    <t>iPhone 19</t>
+  </si>
+  <si>
+    <t>258GB</t>
+  </si>
+  <si>
+    <t>iPhone 20</t>
+  </si>
+  <si>
+    <t>259GB</t>
+  </si>
+  <si>
+    <t>iPhone 21</t>
+  </si>
+  <si>
+    <t>260GB</t>
+  </si>
+  <si>
+    <t>iPhone 22</t>
+  </si>
+  <si>
+    <t>261GB</t>
+  </si>
+  <si>
+    <t>iPhone 23</t>
+  </si>
+  <si>
+    <t>262GB</t>
   </si>
 </sst>
 </file>
@@ -703,10 +736,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1083,7 +1119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="120" spans="1:6">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1097,13 +1133,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="2">
-        <v>63000</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>63400</v>
+      </c>
+      <c r="F2" s="3">
+        <v>5.3371199834303e+18</v>
       </c>
     </row>
-    <row r="3" ht="120" spans="1:6">
+    <row r="3" ht="45" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1114,49 +1150,116 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2">
         <v>64100</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2">
+        <v>64101</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>64102</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2">
+        <v>64103</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2">
+        <v>64104</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2">
+        <v>64105</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2">
+        <v>64106</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>Model</t>
   </si>
@@ -1097,6 +1097,7 @@
     <col min="1" max="1" width="14.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="13.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="12.8571428571429"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1159,7 +1160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" ht="45" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1175,8 +1176,11 @@
       <c r="E4" s="2">
         <v>64101</v>
       </c>
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" ht="45" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -1192,8 +1196,11 @@
       <c r="E5" s="2">
         <v>64102</v>
       </c>
+      <c r="F5" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" ht="45" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -1209,8 +1216,11 @@
       <c r="E6" s="2">
         <v>64103</v>
       </c>
+      <c r="F6" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" ht="45" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -1226,8 +1236,11 @@
       <c r="E7" s="2">
         <v>64104</v>
       </c>
+      <c r="F7" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" ht="45" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1243,8 +1256,11 @@
       <c r="E8" s="2">
         <v>64105</v>
       </c>
+      <c r="F8" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" ht="45" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1259,6 +1275,9 @@
       </c>
       <c r="E9" s="2">
         <v>64106</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Model</t>
   </si>
@@ -61,45 +61,6 @@
   <si>
     <t>White</t>
   </si>
-  <si>
-    <t>5337119983430304580</t>
-  </si>
-  <si>
-    <t>iPhone 18</t>
-  </si>
-  <si>
-    <t>257GB</t>
-  </si>
-  <si>
-    <t>iPhone 19</t>
-  </si>
-  <si>
-    <t>258GB</t>
-  </si>
-  <si>
-    <t>iPhone 20</t>
-  </si>
-  <si>
-    <t>259GB</t>
-  </si>
-  <si>
-    <t>iPhone 21</t>
-  </si>
-  <si>
-    <t>260GB</t>
-  </si>
-  <si>
-    <t>iPhone 22</t>
-  </si>
-  <si>
-    <t>261GB</t>
-  </si>
-  <si>
-    <t>iPhone 23</t>
-  </si>
-  <si>
-    <t>262GB</t>
-  </si>
 </sst>
 </file>
 
@@ -111,7 +72,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +87,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
@@ -598,137 +565,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -736,13 +703,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1137,10 +1102,10 @@
         <v>63400</v>
       </c>
       <c r="F2" s="3">
-        <v>5.3371199834303e+18</v>
+        <v>5.33686069195967e+18</v>
       </c>
     </row>
-    <row r="3" ht="45" spans="1:6">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1156,129 +1121,57 @@
       <c r="E3" s="2">
         <v>64100</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
+      <c r="F3" s="3">
+        <v>5.33954706085934e+18</v>
       </c>
     </row>
-    <row r="4" ht="45" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <v>64101</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
     </row>
-    <row r="5" ht="45" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2">
-        <v>64102</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
     </row>
-    <row r="6" ht="45" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2">
-        <v>64103</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
     </row>
-    <row r="7" ht="45" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2">
-        <v>64104</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
     </row>
-    <row r="8" ht="45" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2">
-        <v>64105</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
     </row>
-    <row r="9" ht="45" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2">
-        <v>64106</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Model</t>
   </si>
@@ -59,7 +59,13 @@
     <t>Blue</t>
   </si>
   <si>
+    <t>5336803891017189390</t>
+  </si>
+  <si>
     <t>White</t>
+  </si>
+  <si>
+    <t>5334808002534860000</t>
   </si>
 </sst>
 </file>
@@ -695,7 +701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -703,13 +709,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1056,13 +1065,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="13.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="12.8571428571429"/>
+    <col min="6" max="6" width="28.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1101,8 +1110,8 @@
       <c r="E2" s="2">
         <v>63400</v>
       </c>
-      <c r="F2" s="3">
-        <v>5.33686069195967e+18</v>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1116,62 +1125,65 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2">
         <v>64100</v>
       </c>
-      <c r="F3" s="3">
-        <v>5.33954706085934e+18</v>
+      <c r="F3" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="6:6">
+      <c r="F10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
